--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -1,37 +1,181 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/Pycharm/Nike/J30/Output_files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD5AD9C-7EFC-C742-89AC-FAC0FB52D2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="49260" yWindow="4220" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ItemSearchResult" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ItemSearchResult" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="44">
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>DimsUOM</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>VolumeUOM</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>WeightUOM</t>
+  </si>
+  <si>
+    <t>PrimaryBarCode</t>
+  </si>
+  <si>
+    <t>DivisionCode</t>
+  </si>
+  <si>
+    <t>MarkforCubiScan</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>1081</t>
+  </si>
+  <si>
+    <t>123456-001-TST</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>cucm</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>00000100479248</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>DEMOTST-001-TST</t>
+  </si>
+  <si>
+    <t>10000000001234</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
+    <t>00887231717408</t>
+  </si>
+  <si>
+    <t>420420-420-M</t>
+  </si>
+  <si>
+    <t>1234567891</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>DN0560-885-6</t>
+  </si>
+  <si>
+    <t>00195240735536</t>
+  </si>
+  <si>
+    <t>DN0560-822-6</t>
+  </si>
+  <si>
+    <t>00196152285461</t>
+  </si>
+  <si>
+    <t>DD9293-100-7</t>
+  </si>
+  <si>
+    <t>00195870855925</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>DD9293-100-12.5</t>
+  </si>
+  <si>
+    <t>00195870856038</t>
+  </si>
+  <si>
+    <t>DD9293-100-10</t>
+  </si>
+  <si>
+    <t>00195870855987</t>
+  </si>
+  <si>
+    <t>Apparel</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Footwear</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +190,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,199 +514,486 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ItemId</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>DimsUOM</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>VolumeUOM</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>WeightUOM</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>PrimaryBarCode</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>DivisionCode</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>MarkforCubiScan</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>924156-836-M</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>00194274914153</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>924156-319-S</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>00193654264659</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>924156-836-S</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>00194274914146</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3">
+        <v>64</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3">
+        <v>0.8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <v>5760</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4">
+        <v>0.8</v>
+      </c>
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <v>24.8</v>
+      </c>
+      <c r="E6">
+        <v>23.4</v>
+      </c>
+      <c r="F6">
+        <v>22.7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6">
+        <v>13173.263999999999</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="K6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>24.8</v>
+      </c>
+      <c r="E7">
+        <v>23.4</v>
+      </c>
+      <c r="F7">
+        <v>22.7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>13173.263999999999</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>19.5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>4719</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>0.4</v>
+      </c>
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F9">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9">
+        <v>3484.8</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="K9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="E10">
+        <v>16.2</v>
+      </c>
+      <c r="F10">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10">
+        <v>15177.78</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="K10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="W11" t="s">
+        <v>41</v>
+      </c>
+      <c r="X11">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="W12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X12">
+        <v>20</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="W13" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/Pycharm/Nike/J30/Output_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD5AD9C-7EFC-C742-89AC-FAC0FB52D2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70C4CA6-738C-7A48-A6DB-7DD3FEB7ED0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49260" yWindow="4220" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="102400" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemSearchResult" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="41">
   <si>
     <t>Environment</t>
   </si>
@@ -85,7 +85,7 @@
     <t>00000100479248</t>
   </si>
   <si>
-    <t>10</t>
+    <t>Apparel</t>
   </si>
   <si>
     <t>Y</t>
@@ -109,7 +109,7 @@
     <t>1234567891</t>
   </si>
   <si>
-    <t>30</t>
+    <t>Equipment</t>
   </si>
   <si>
     <t>DN0560-885-6</t>
@@ -130,7 +130,7 @@
     <t>00195870855925</t>
   </si>
   <si>
-    <t>20</t>
+    <t>Footwear</t>
   </si>
   <si>
     <t>DD9293-100-12.5</t>
@@ -143,15 +143,6 @@
   </si>
   <si>
     <t>00195870855987</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>Footwear</t>
   </si>
 </sst>
 </file>
@@ -515,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -534,7 +525,7 @@
     <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -578,7 +569,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -622,7 +613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -663,7 +654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -704,7 +695,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -745,7 +736,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -789,7 +780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -833,7 +824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -877,7 +868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -921,7 +912,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -963,36 +954,6 @@
       </c>
       <c r="N10" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="W11" t="s">
-        <v>41</v>
-      </c>
-      <c r="X11">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="W12" t="s">
-        <v>42</v>
-      </c>
-      <c r="X12">
-        <v>20</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="W13" t="s">
-        <v>43</v>
-      </c>
-      <c r="X13">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D590B9A7-E513-5A49-ACD8-36280E683883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6229A671-1983-5B42-8106-CED43CF2772D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7280" yWindow="5280" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemSearchResult" sheetId="1" r:id="rId1"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB871263-AA38-F241-A1B9-F7C9DAC14594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8E2417-1E31-FC40-91BF-CA21E4B4B70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="68180" yWindow="7380" windowWidth="36000" windowHeight="23380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemSearchResult" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Environment</t>
   </si>
@@ -70,79 +70,25 @@
     <t>1081</t>
   </si>
   <si>
-    <t>924156-365-XS</t>
-  </si>
-  <si>
-    <t>cm</t>
-  </si>
-  <si>
-    <t>cucm</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>00196605116724</t>
+    <t>924156-365-M</t>
+  </si>
+  <si>
+    <t>00196605116748</t>
   </si>
   <si>
     <t>Apparel</t>
   </si>
   <si>
-    <t>924157-417-S</t>
-  </si>
-  <si>
-    <t>00193654265809</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>924157-450-L</t>
-  </si>
-  <si>
-    <t>00196152790033</t>
-  </si>
-  <si>
-    <t>AC3894-443-MISC</t>
-  </si>
-  <si>
-    <t>00193655382123</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>AC3894-740-MISC</t>
-  </si>
-  <si>
-    <t>00193654541279</t>
-  </si>
-  <si>
-    <t>AC4081-823-MISC</t>
-  </si>
-  <si>
-    <t>00193654541361</t>
-  </si>
-  <si>
-    <t>DD9293-401-11</t>
-  </si>
-  <si>
-    <t>00196153286290</t>
-  </si>
-  <si>
-    <t>Footwear</t>
-  </si>
-  <si>
-    <t>DD9293-401-14</t>
-  </si>
-  <si>
-    <t>00196153286344</t>
-  </si>
-  <si>
-    <t>DD9293-401-13</t>
-  </si>
-  <si>
-    <t>00196153286337</t>
+    <t>924157-417-2XL</t>
+  </si>
+  <si>
+    <t>00195868982152</t>
+  </si>
+  <si>
+    <t>924156-836-XL</t>
+  </si>
+  <si>
+    <t>00194274914177</t>
   </si>
 </sst>
 </file>
@@ -506,17 +452,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -580,34 +526,13 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
         <v>17</v>
       </c>
-      <c r="H2">
-        <v>180</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>18</v>
-      </c>
-      <c r="J2">
-        <v>0.3</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -618,40 +543,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3">
-        <v>180</v>
-      </c>
-      <c r="I3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
         <v>18</v>
-      </c>
-      <c r="J3">
-        <v>0.3</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -662,295 +563,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4">
-        <v>180</v>
-      </c>
-      <c r="I4" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
         <v>18</v>
-      </c>
-      <c r="J4">
-        <v>0.3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5">
-        <v>4.5</v>
-      </c>
-      <c r="E5">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>4.5</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5">
-        <v>475</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6">
-        <v>4.5</v>
-      </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>4.5</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6">
-        <v>475</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
-      <c r="E7">
-        <v>11.1</v>
-      </c>
-      <c r="F7">
-        <v>11.5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>2403.5</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8">
-        <v>36.5</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>24.5</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>11625.25</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="K8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" t="s">
-        <v>36</v>
-      </c>
-      <c r="N8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9">
-        <v>36</v>
-      </c>
-      <c r="E9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F9">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9">
-        <v>3801.6</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9">
-        <v>0.998</v>
-      </c>
-      <c r="K9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10">
-        <v>36.9</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10">
-        <v>22.9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10">
-        <v>2535.0300000000002</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10">
-        <v>0.95399999999999996</v>
-      </c>
-      <c r="K10" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -1,118 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Output_files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8E2417-1E31-FC40-91BF-CA21E4B4B70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="68180" yWindow="7380" windowWidth="36000" windowHeight="23380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ItemSearchResult" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemSearchResult" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>ItemId</t>
-  </si>
-  <si>
-    <t>Length</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t>DimsUOM</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>VolumeUOM</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>WeightUOM</t>
-  </si>
-  <si>
-    <t>PrimaryBarCode</t>
-  </si>
-  <si>
-    <t>DivisionCode</t>
-  </si>
-  <si>
-    <t>MarkforCubiScan</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>924156-365-M</t>
-  </si>
-  <si>
-    <t>00196605116748</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
-    <t>924157-417-2XL</t>
-  </si>
-  <si>
-    <t>00195868982152</t>
-  </si>
-  <si>
-    <t>924156-836-XL</t>
-  </si>
-  <si>
-    <t>00194274914177</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -127,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -451,129 +420,237 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ItemId</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>DimsUOM</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>VolumeUOM</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WeightUOM</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>PrimaryBarCode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>DivisionCode</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>MarkforCubiScan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>924156-459-S</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00196155922271</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>924156-404-L</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00193146310314</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>924156-319-2XL</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" t="s">
-        <v>18</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00195870867294</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>924156-365-S</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" t="s">
-        <v>18</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00196605116731</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>924156-459-S</t>
+          <t>924156-391-XS</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -528,7 +528,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00196155922271</t>
+          <t>00194274913538</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>924156-404-L</t>
+          <t>924156-342-XS</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -566,7 +566,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00193146310314</t>
+          <t>00195867427173</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>924156-319-2XL</t>
+          <t>DM0825-600-4</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -604,12 +604,12 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>00195870867294</t>
+          <t>00196154175463</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>924156-365-S</t>
+          <t>DM2385-101-18</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -642,15 +642,91 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>00196605116731</t>
+          <t>00196155017373</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DH6619-010-1</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00196155790306</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DH6619-010-5</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00196155790344</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,11 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ProductClass</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>MarkforCubiScan</t>
         </is>
       </c>
@@ -513,22 +518,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>924156-391-XS</t>
+          <t>DEMOTST-001-TST</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>64</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00194274913538</t>
+          <t>10000000001234</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -536,7 +561,12 @@
           <t>Apparel</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,30 +581,55 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>924156-342-XS</t>
+          <t>102030-003-MISC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00195867427173</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Apparel</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>00000001238375</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,22 +644,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DM0825-600-4</t>
+          <t>319986-045-10</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>10323.25</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>00196154175463</t>
+          <t>00193145560888</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -612,7 +687,12 @@
           <t>Footwear</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -627,22 +707,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DM2385-101-18</t>
+          <t>315122-111-10</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>34.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>9881.76</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>00196155017373</t>
+          <t>00883412740937</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -650,83 +750,16 @@
           <t>Footwear</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DH6619-010-1</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>00196155790306</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DH6619-010-5</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>00196155790344</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,42 +518,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEMOTST-001-TST</t>
+          <t>829748-010-S</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>64</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10000000001234</t>
+          <t>00887229001281</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -561,11 +541,7 @@
           <t>Apparel</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -581,185 +557,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>102030-003-MISC</t>
+          <t>829747-091-XL</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00000001238375</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>319986-045-10</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>10323.25</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>00193145560888</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Footwear</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Footwear</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>315122-111-10</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>24</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>9881.76</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>00883412740937</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Footwear</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Footwear</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>00887228794108</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -1,37 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Output_files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042DD3BF-E6C2-AA4F-9E40-CC0B775936F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="59840" yWindow="14420" windowWidth="28480" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemSearchResult" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ItemSearchResult" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>DimsUOM</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>VolumeUOM</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>WeightUOM</t>
+  </si>
+  <si>
+    <t>PrimaryBarCode</t>
+  </si>
+  <si>
+    <t>DivisionCode</t>
+  </si>
+  <si>
+    <t>ProductClass</t>
+  </si>
+  <si>
+    <t>MarkforCubiScan</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>1081</t>
+  </si>
+  <si>
+    <t>829748-010-XS</t>
+  </si>
+  <si>
+    <t>00887229001274</t>
+  </si>
+  <si>
+    <t>Apparel</t>
+  </si>
+  <si>
+    <t>829748-010-M</t>
+  </si>
+  <si>
+    <t>00887229001410</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +124,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,168 +448,113 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ItemId</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>DimsUOM</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>VolumeUOM</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>WeightUOM</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>PrimaryBarCode</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>DivisionCode</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ProductClass</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>MarkforCubiScan</t>
-        </is>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>829748-010-S</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>00887229001281</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Apparel</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>829747-091-XL</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>00887228794108</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Apparel</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -1,115 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Output_files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042DD3BF-E6C2-AA4F-9E40-CC0B775936F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="59840" yWindow="14420" windowWidth="28480" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ItemSearchResult" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemSearchResult" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>ItemId</t>
-  </si>
-  <si>
-    <t>Length</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t>DimsUOM</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>VolumeUOM</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>WeightUOM</t>
-  </si>
-  <si>
-    <t>PrimaryBarCode</t>
-  </si>
-  <si>
-    <t>DivisionCode</t>
-  </si>
-  <si>
-    <t>ProductClass</t>
-  </si>
-  <si>
-    <t>MarkforCubiScan</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>829748-010-XS</t>
-  </si>
-  <si>
-    <t>00887229001274</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
-    <t>829748-010-M</t>
-  </si>
-  <si>
-    <t>00887229001410</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -124,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -448,113 +420,168 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ItemId</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>DimsUOM</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>VolumeUOM</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WeightUOM</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>PrimaryBarCode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>DivisionCode</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProductClass</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>MarkforCubiScan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>829748-010-M</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00887229001410</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>829747-091-L-T</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00887223899822</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>829748-010-M</t>
+          <t>829748-010-XL</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -533,7 +533,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00887229001410</t>
+          <t>00887229001434</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>829747-091-L-T</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -572,7 +572,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00887223899822</t>
+          <t>00887231075027</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>829748-010-XL</t>
+          <t>829747-091-3XL</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -533,7 +533,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00887229001434</t>
+          <t>00887231075027</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>829747-091-3XL</t>
+          <t>829747-091-CUST4</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -572,7 +572,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00887231075027</t>
+          <t>00887223899853</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>829747-091-3XL</t>
+          <t>924161-021-S</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -533,7 +533,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00887231075027</t>
+          <t>00193654267957</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>829747-091-CUST4</t>
+          <t>924161-021-2XL</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -572,7 +572,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00887223899853</t>
+          <t>00195868982442</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -518,31 +518,55 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>924161-021-S</t>
+          <t>DD9293-100-11.5</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>10368</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00193654267957</t>
+          <t>00195870856014</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -557,27 +581,47 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>924161-021-2XL</t>
+          <t>DD9293-100-6</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3360</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00195868982442</t>
+          <t>00195870855901</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -518,55 +518,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DD9293-100-11.5</t>
+          <t>924161-021-M</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>10368</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.872</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00195870856014</t>
+          <t>00193654267964</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Apparel</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -581,47 +557,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DD9293-100-6</t>
+          <t>924161-021-L</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>28</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>3360</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00195870855901</t>
+          <t>00193654267971</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Apparel</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>924161-021-M</t>
+          <t>924157-417-XL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00193654267964</t>
+          <t>00193654265830</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -557,22 +577,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>924161-021-L</t>
+          <t>924157-450-XL</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00193654267971</t>
+          <t>00196152790040</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -582,6 +622,250 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AC4081-451-MISC</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2403.5</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00193654541323</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AC4081-451-1SIZE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>108</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DD9293-100-12</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>16370.25</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00195870856021</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DD9293-100-9</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>27</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>15177.78</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.08019999999999999</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00195870855963</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,42 +518,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>924157-417-XL</t>
+          <t>829747-091-2XL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00193654265830</t>
+          <t>00887231075010</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -563,309 +543,6 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>924157-450-XL</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>20</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>00196152790040</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Apparel</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AC4081-451-MISC</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>2403.5</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>00193654541323</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AC4081-451-1SIZE</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>108</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DD9293-100-12</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>13</v>
-      </c>
-      <c r="F6" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>16370.25</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>00195870856021</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Footwear</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DD9293-100-9</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>27</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>15177.78</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.08019999999999999</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>00195870855963</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Footwear</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,31 +518,118 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>829747-091-2XL</t>
+          <t>DC4244-291-MISC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>9865</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00887231075010</t>
+          <t>00196968859245</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DC4244-328-MISC</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>24</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>9865</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00196968859252</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,17 +518,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DC4244-291-MISC</t>
+          <t>848196-885-L</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>25.2</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>30.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9865</v>
+        <v>3750</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -553,12 +553,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00196968859245</t>
+          <t>00196968515356</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Apparel</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -581,17 +581,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DC4244-328-MISC</t>
+          <t>909746-323-M</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>9865</v>
+        <v>2000</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -616,16 +616,268 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00196968859252</t>
+          <t>00884776344014</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Apparel</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CJ2242-113-M</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4476.576</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00194502804256</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CJ2242-113-2XL</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10558.08</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00194502804287</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CJ2242-113-L</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2657.545</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00194502804263</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CJ2242-140-M</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>4476.576</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00194495899505</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,55 +518,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>848196-885-L</t>
+          <t>343738-031-1Y</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3750</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00196968515356</t>
+          <t>00198484266255</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -581,55 +557,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>909746-323-M</t>
+          <t>343738-031-2Y</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>20</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00884776344014</t>
+          <t>00198484266354</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -644,55 +596,31 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CJ2242-113-M</t>
+          <t>343738-031-11C</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4476.576</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>00194502804256</t>
+          <t>00198484267184</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -707,55 +635,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CJ2242-113-2XL</t>
+          <t>343738-031-12C</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>10558.08</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>00194502804287</t>
+          <t>00198484268969</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -770,55 +674,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CJ2242-113-L</t>
+          <t>343738-031-1.5Y</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2657.545</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>00194502804263</t>
+          <t>00198484273734</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -833,55 +713,6313 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CJ2242-140-M</t>
+          <t>343738-031-11.5C</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F7" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="G7" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00198484276087</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>343738-031-12.5C</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>00198484281654</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>343738-031-13C</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>00198484285171</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>343738-031-10.5C</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>00198484287304</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>343738-031-13.5C</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>00198484290595</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>343738-031-3Y</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>00198484291851</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>343738-031-2.5Y</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>00198484293626</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>343880-202-6</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>00193154121612</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>343880-202-7</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>00193154121629</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>343880-202-8</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>00193154121636</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>343880-202-9</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>00193154121643</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>343880-202-10</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>00193154121650</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>343880-202-11</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>00193154121667</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>343880-202-12</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>00193154121674</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>343880-202-13</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>00193154121681</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>343880-202-14</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>00193154121698</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>343880-202-15</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>00193154121704</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>343881-011-5</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>4476.576</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H24" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>cucm</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>00194495899505</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Apparel</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>00659658280847</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>343881-011-6</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>00659658280854</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>343881-011-7</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>23</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>38</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>6118</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>00659658280861</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>343881-011-8</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>00659658280878</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>343881-011-9</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>00659658280922</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>343881-011-10</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>00659658280939</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>343881-011-11</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E30" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>16650</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>00659658280946</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>343881-011-12</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>00659658280953</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>343881-011-4</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>00887231283729</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>343881-011-13</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>00887231283736</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>343881-011-14</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>00887231283743</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>343881-011-15</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>00887231283750</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>343881-011-16</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>00887231283767</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>343881-011-17</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>00887231283774</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>343881-011-18</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>00887231283781</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>343938-031-3C</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>00198484267054</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>343938-031-9C</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>00198484269430</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>343938-031-6C</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>00198484272409</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>343938-031-10C</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>00198484272683</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>343938-031-2C</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>00198484274182</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>343938-031-8C</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>00198484281869</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>343938-031-5C</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>00198484283214</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>343938-031-4C</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>00198484284594</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>343938-031-7C</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>00198484287205</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>355152-106-6</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>00091201843701</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>355152-106-6.5</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>00091201843718</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>355152-106-7</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>00091201843725</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>355152-106-7.5</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>00091201843732</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>355152-106-8</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>00091201844326</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>355152-106-8.5</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>00091201844340</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>355152-106-9</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>00091201844951</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>355152-106-9.5</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>00091201845484</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>355152-106-10</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>00091201845507</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>355152-106-10.5</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>00091201845583</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>355152-106-11</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>00091201845941</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>355152-106-11.5</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>00091201845972</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>355152-106-12</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>00091201845989</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>355152-106-12.5</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>00091201845996</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>355152-106-13</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>00091201846009</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>355152-106-14</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>00091201846061</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>355152-106-15</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>00091201846078</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>355152-140-6</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>00091201846085</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>355152-140-6.5</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>00091201846092</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>355152-140-7</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>00091201846269</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>355152-140-7.5</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>00091201847556</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>355152-140-8</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>00091201847761</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>355152-140-8.5</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>00091201847778</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>355152-140-9</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>00091201847785</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>355152-140-9.5</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>00091201848096</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>355152-140-10</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>00091201858187</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>355152-140-10.5</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>00091201858194</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>355152-140-11</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>00091201858200</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>355152-140-11.5</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>00091201858217</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>355152-140-12</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>00091201858231</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>355152-140-12.5</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>00091201858255</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>355152-140-13</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>00091201858279</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>355152-140-14</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>00091201858293</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>355152-140-15</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>00091201858668</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>394055-100-6</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>00194274672978</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>394055-100-6.5</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>30</v>
+      </c>
+      <c r="E83" t="n">
+        <v>22</v>
+      </c>
+      <c r="F83" t="n">
+        <v>27</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>17820</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>00194274672985</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>394055-100-7</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>00194274672992</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>394055-100-7.5</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>00194274673005</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>394055-100-8</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>00194274673012</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>394055-100-8.5</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>00194274673029</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>394055-100-9</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>00123456253551</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>394055-100-9.5</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>00194274673043</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>394055-100-10</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E90" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F90" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>10158.078</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>00194274673050</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>394055-100-10.5</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>00194274673067</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>394055-100-11</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>00194274673074</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>394055-100-11.5</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>00194274673081</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>394055-100-12</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>00194274673098</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>394055-100-12.5</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>00194274673104</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>394055-100-13</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E96" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F96" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>13286.871</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>00194274673111</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>394055-100-14</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>00194274673128</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>394055-100-15</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>00194274673135</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>415082-002-3.5Y</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>00886549587727</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>415082-002-4Y</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>00886549587734</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>415082-002-4.5Y</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>00886549587741</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>415082-002-5Y</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>00886549587758</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>415082-002-5.5Y</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>00886549587765</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>415082-002-6Y</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>00886549588038</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>415082-002-6.5Y</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>00886549589042</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>415082-002-7Y</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>00886549589066</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>432997-121-6</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>00193152581982</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>432997-121-6.5</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>00193152581999</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>432997-121-7</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>00193152582002</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>432997-121-7.5</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>00193152582019</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>432997-121-8</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>00193152582026</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>432997-121-8.5</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>00193152582033</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>432997-121-9</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>00193152582040</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>432997-121-9.5</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>00193152582057</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>432997-121-10</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>00193152582064</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>432997-121-10.5</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>00193152582071</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>432997-121-11</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>00193152582088</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>432997-121-11.5</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>00193152582095</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>432997-121-12</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>00193152582101</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>432997-121-12.5</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>00193152582118</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>432997-121-13</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>00193152582125</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>432997-121-14</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>00193152582132</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>432997-121-15</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>00193152582149</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>432997-128-6</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>00194276397084</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>432997-128-6.5</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>00194276397091</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>432997-128-7</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>00194276397107</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>432997-128-7.5</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>00194276397114</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>432997-128-8</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>00194276397121</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>432997-128-8.5</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>00194276397138</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>432997-128-9</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>00194276397145</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>432997-128-9.5</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>00194276397152</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>432997-128-10</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>00194276397169</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>432997-128-10.5</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>00194276397176</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>432997-128-11</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>00194276397183</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>432997-128-11.5</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>00194276397190</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>432997-128-12</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>00194276397206</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>432997-128-12.5</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>00194276397213</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>432997-128-15</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>00194276397244</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>487754-408-6</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>00193145415836</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>487754-408-6.5</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>00193145415843</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>487754-408-7</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>00193145415850</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>487754-408-7.5</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>00193145415867</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>487754-408-8</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>00193145415874</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>487754-408-8.5</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>00193145415881</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>487754-408-9</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>00193145415898</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>487754-408-9.5</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>00193145415904</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>487754-408-10</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>00193145415911</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>487754-408-10.5</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>00193145415928</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>487754-408-11</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>00193145415935</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>487754-408-11.5</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>00193145415942</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>487754-408-12</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>00193145415959</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>487754-408-12.5</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>00193145415966</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>487754-408-13</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>00193145415973</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>487754-408-14</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>00193145415980</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>487754-408-15</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>00193145415997</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>487754-408-4.5</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>00197861690720</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>487754-408-5.5</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>00197861919340</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>487754-408-5</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>00197861516013</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>487754-408-4</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>00197861631600</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>II5196-031-MISC</t>
+          <t>343738-013-13.5C</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -543,12 +543,12 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00198485551022</t>
+          <t>00091206961257</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>II5196-405-MISC</t>
+          <t>343738-013-12.5C</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -584,12 +584,12 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00198485553491</t>
+          <t>00091206961233</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PBZ182-011-MISC</t>
+          <t>343738-013-11.5C</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -625,18 +625,1903 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>00196976370213</t>
+          <t>00091206961219</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>343738-013-3Y</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00091206961639</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>343738-013-2Y</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>7488</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00091206961530</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>343738-013-2.5Y</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00091206961622</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>343738-013-12C</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>00091206961226</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>343738-013-1.5Y</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>00091206961271</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>343738-013-10.5C</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>00091206961097</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>343738-013-1Y</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>00091206961264</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>343738-013-11C</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>00091206961103</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>343738-013-13C</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>00091206961240</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>343738-031-1Y</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>00198484266255</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>343738-031-2.5Y</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>00198484293626</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>343738-031-12.5C</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>00198484281654</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>343738-031-12C</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>00198484268969</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>343738-031-2Y</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>00198484266354</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>343738-031-13C</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>00198484285171</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>343738-031-10.5C</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>00198484287304</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>343738-031-3Y</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>00198484291851</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>343738-031-11C</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>00198484267184</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>343738-031-1.5Y</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>00198484273734</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>343738-031-11.5C</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>00198484276087</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>343738-031-13.5C</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>00198484290595</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>343738-106-13C</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>00197863545981</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>343738-106-2Y</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>00197863559087</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>343738-106-1.5Y</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>00197863518619</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>343738-106-10.5C</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>00197863486673</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>343738-106-3Y</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>00197863559872</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>343738-106-1Y</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>00197863502915</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>343738-106-2.5Y</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>00197863538617</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>343738-106-12C</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>00197863487397</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>343738-106-11C</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>00197863486604</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>343738-106-12.5C</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>00197863497341</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>343738-106-13.5C</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>00197863535951</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>343738-106-11.5C</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>00197863491509</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>343738-809-2.5Y</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>00197863464046</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>343738-809-13.5C</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>00197863469126</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>343738-809-11.5C</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>00197863468464</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>343738-809-13C</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>00197863467771</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>343738-809-2Y</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>00197863465913</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>343738-809-3Y</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>00197863464169</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>343738-809-10.5C</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>00197863465241</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>343738-809-12.5C</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>00197863469713</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>343738-809-1Y</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>00197863469782</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>343738-809-11C</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>00197863467733</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>343738-809-1.5Y</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>00197863464565</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>343738-809-12C</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>00197863464848</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/J30/Output_files/item_search_results.xlsx
+++ b/J30/Output_files/item_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>343738-013-13.5C</t>
+          <t>SX5728-010-XS</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -543,12 +543,12 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00091206961257</t>
+          <t>00091209472934</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>343738-013-12.5C</t>
+          <t>SX5728-010-S</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -584,12 +584,12 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00091206961233</t>
+          <t>00091209472941</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>343738-013-11.5C</t>
+          <t>SX5728-010-M</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -625,20 +625,16 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>00091206961219</t>
+          <t>00091209472958</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -655,7 +651,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>343738-013-3Y</t>
+          <t>SX5728-010-L</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -670,12 +666,12 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>00091206961639</t>
+          <t>00091209496558</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -696,47 +692,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>343738-013-2Y</t>
+          <t>SX5728-010-XL</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>7488</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>cucm</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>00091206961530</t>
+          <t>00091209500590</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -757,7 +733,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>343738-013-2.5Y</t>
+          <t>SX5728-100-XS</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -772,12 +748,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>00091206961622</t>
+          <t>00091209517369</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -798,7 +774,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>343738-013-12C</t>
+          <t>SX5728-100-S</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -813,12 +789,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>00091206961226</t>
+          <t>00091209517376</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -839,7 +815,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>343738-013-1.5Y</t>
+          <t>SX5728-100-M</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -854,12 +830,12 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>00091206961271</t>
+          <t>00091209517383</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -880,7 +856,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>343738-013-10.5C</t>
+          <t>SX5728-100-L</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -895,12 +871,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>00091206961097</t>
+          <t>00091209517659</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -921,7 +897,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>343738-013-1Y</t>
+          <t>SX5728-100-XL</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -936,20 +912,16 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>00091206961264</t>
+          <t>00091209517666</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
@@ -966,7 +938,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>343738-013-11C</t>
+          <t>SX5728-302-XS</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -981,12 +953,12 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>00091206961103</t>
+          <t>00091209530191</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1007,7 +979,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>343738-013-13C</t>
+          <t>SX5728-302-S</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1022,12 +994,12 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>00091206961240</t>
+          <t>00091209530252</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1048,7 +1020,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>343738-031-1Y</t>
+          <t>SX5728-302-M</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1063,20 +1035,16 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>00198484266255</t>
+          <t>00091209530382</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -1093,7 +1061,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>343738-031-2.5Y</t>
+          <t>SX5728-302-L</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1108,12 +1076,12 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>00198484293626</t>
+          <t>00091209532034</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1134,7 +1102,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>343738-031-12.5C</t>
+          <t>SX5728-302-XL</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1149,12 +1117,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>00198484281654</t>
+          <t>00091209532447</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1175,7 +1143,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>343738-031-12C</t>
+          <t>SX5728-411-XS</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1190,12 +1158,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>00198484268969</t>
+          <t>00091209543382</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1216,7 +1184,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>343738-031-2Y</t>
+          <t>SX5728-411-S</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1231,12 +1199,12 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>00198484266354</t>
+          <t>00091209543436</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1257,7 +1225,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>343738-031-13C</t>
+          <t>SX5728-411-M</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1272,12 +1240,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>00198484285171</t>
+          <t>00091209544037</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -1298,7 +1266,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>343738-031-10.5C</t>
+          <t>SX5728-411-L</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1313,12 +1281,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>00198484287304</t>
+          <t>00091209544044</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1339,7 +1307,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>343738-031-3Y</t>
+          <t>SX5728-411-XL</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1354,12 +1322,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>00198484291851</t>
+          <t>00091209547281</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -1380,7 +1348,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>343738-031-11C</t>
+          <t>SX5728-412-XS</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1395,12 +1363,12 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>00198484267184</t>
+          <t>00091209549773</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1421,7 +1389,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>343738-031-1.5Y</t>
+          <t>SX5728-412-S</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1436,12 +1404,12 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>00198484273734</t>
+          <t>00091209550274</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -1462,7 +1430,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>343738-031-11.5C</t>
+          <t>SX5728-412-M</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1477,12 +1445,12 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>00198484276087</t>
+          <t>00091209550670</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1503,7 +1471,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>343738-031-13.5C</t>
+          <t>SX5728-412-L</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1518,12 +1486,12 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>00198484290595</t>
+          <t>00091209553671</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -1544,7 +1512,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>343738-106-13C</t>
+          <t>SX5728-412-XL</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1559,12 +1527,12 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>00197863545981</t>
+          <t>00091209555118</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -1585,7 +1553,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>343738-106-2Y</t>
+          <t>SX5728-448-XS</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1600,12 +1568,12 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>00197863559087</t>
+          <t>00091209557723</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -1626,7 +1594,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>343738-106-1.5Y</t>
+          <t>SX5728-448-S</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1641,12 +1609,12 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>00197863518619</t>
+          <t>00091209557778</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -1667,7 +1635,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>343738-106-10.5C</t>
+          <t>SX5728-448-M</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1682,12 +1650,12 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>00197863486673</t>
+          <t>00091209557945</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -1708,7 +1676,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>343738-106-3Y</t>
+          <t>SX5728-448-L</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1723,12 +1691,12 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>00197863559872</t>
+          <t>00091209557952</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -1749,7 +1717,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>343738-106-1Y</t>
+          <t>SX5728-448-XL</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1764,20 +1732,16 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>00197863502915</t>
+          <t>00091209558409</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -1794,7 +1758,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>343738-106-2.5Y</t>
+          <t>SX5728-463-XS</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1809,12 +1773,12 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>00197863538617</t>
+          <t>00091209562741</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -1835,7 +1799,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>343738-106-12C</t>
+          <t>SX5728-463-S</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1850,12 +1814,12 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>00197863487397</t>
+          <t>00091209562758</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -1876,7 +1840,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>343738-106-11C</t>
+          <t>SX5728-463-M</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1891,12 +1855,12 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>00197863486604</t>
+          <t>00091209562765</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -1917,7 +1881,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>343738-106-12.5C</t>
+          <t>SX5728-463-L</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1932,12 +1896,12 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>00197863497341</t>
+          <t>00091209562789</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -1958,7 +1922,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>343738-106-13.5C</t>
+          <t>SX5728-463-XL</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1973,12 +1937,12 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>00197863535951</t>
+          <t>00091209571958</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -1999,7 +1963,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>343738-106-11.5C</t>
+          <t>SX5728-648-XS</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2014,12 +1978,12 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>00197863491509</t>
+          <t>00091209574799</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2040,7 +2004,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>343738-809-2.5Y</t>
+          <t>SX5728-648-S</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2055,12 +2019,12 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>00197863464046</t>
+          <t>00091209574805</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2081,7 +2045,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>343738-809-13.5C</t>
+          <t>SX5728-648-M</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2096,12 +2060,12 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>00197863469126</t>
+          <t>00091209577349</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2122,7 +2086,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>343738-809-11.5C</t>
+          <t>SX5728-648-L</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2137,12 +2101,12 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>00197863468464</t>
+          <t>00091209577455</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2163,7 +2127,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>343738-809-13C</t>
+          <t>SX5728-648-XL</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2178,12 +2142,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>00197863467771</t>
+          <t>00091209577486</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2204,7 +2168,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>343738-809-2Y</t>
+          <t>SX5728-670-XS</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2219,12 +2183,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>00197863465913</t>
+          <t>00091209579107</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2245,7 +2209,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>343738-809-3Y</t>
+          <t>SX5728-670-S</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2260,12 +2224,12 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>00197863464169</t>
+          <t>00091209579206</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -2286,7 +2250,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>343738-809-10.5C</t>
+          <t>SX5728-670-M</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2301,12 +2265,12 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>00197863465241</t>
+          <t>00091209579220</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -2327,7 +2291,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>343738-809-12.5C</t>
+          <t>SX5728-670-L</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2342,12 +2306,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>00197863469713</t>
+          <t>00091209579404</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -2368,7 +2332,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>343738-809-1Y</t>
+          <t>SX5728-670-XL</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2383,20 +2347,16 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>00197863469782</t>
+          <t>00091209579411</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
     </row>
@@ -2413,7 +2373,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>343738-809-11C</t>
+          <t>SX5728-702-XS</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2428,12 +2388,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>00197863467733</t>
+          <t>00091209579671</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -2454,7 +2414,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>343738-809-1.5Y</t>
+          <t>SX5728-702-S</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2469,12 +2429,12 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>00197863464565</t>
+          <t>00091209584248</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -2495,7 +2455,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>343738-809-12C</t>
+          <t>SX5728-702-M</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2510,12 +2470,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>00197863464848</t>
+          <t>00091209587522</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -2523,6 +2483,1108 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SX5728-702-L</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>00091209588789</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SX5728-702-XL</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>00091209590843</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SX5728-719-XS</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>00193153924665</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SX5728-719-S</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>00193153924672</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SX5728-719-M</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>00193153924689</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SX5728-719-L</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>00193153924696</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SX5728-719-XL</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>00193153924702</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SX5854-010-XS</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>00883418325503</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SX5854-010-S</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>00883418325589</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SX5854-010-M</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>00883418325596</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SX5854-010-L</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>00883418325602</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SX5854-010-XL</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>00883418325619</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SX7622-013-S</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>24</v>
+      </c>
+      <c r="E62" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>20</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>00191885403267</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SX7622-013-M</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>24</v>
+      </c>
+      <c r="E63" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>20</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>00191885403274</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SX7622-013-L</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>24</v>
+      </c>
+      <c r="E64" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>20</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>00191885403281</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SX7622-013-XL</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>24</v>
+      </c>
+      <c r="E65" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>20</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>00191885403298</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SX7622-013-2XL</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>24</v>
+      </c>
+      <c r="E66" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>20</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>00194275600482</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SX7622-100-S</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>24</v>
+      </c>
+      <c r="E67" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>20</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>00191885403342</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SX7622-100-2XL</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>24</v>
+      </c>
+      <c r="E68" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>20</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>00194275600505</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SX7622-100-M</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>24</v>
+      </c>
+      <c r="E69" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>00191885403359</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SX7622-100-L</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>24</v>
+      </c>
+      <c r="E70" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>20</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>00191885403366</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SX7622-100-XL</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>24</v>
+      </c>
+      <c r="E71" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>20</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>10128</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>cucm</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>00191885403373</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
